--- a/T2W/transportation-to-work-dd.xlsx
+++ b/T2W/transportation-to-work-dd.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/T2W/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138CB6AA-6103-C14A-A0B8-FEDB0C66A848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="195" windowWidth="18195" windowHeight="11700"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataDictionary" sheetId="2" r:id="rId1"/>
     <sheet name="MPO-CountyList" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
@@ -658,7 +663,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -779,17 +784,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -815,7 +816,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -828,8 +829,8 @@
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 4" xfId="3"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -837,14 +838,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -882,7 +886,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -954,7 +958,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1127,361 +1131,361 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="35.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="57.7109375" customWidth="1"/>
+    <col min="2" max="2" width="35.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="57.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="8">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="210" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:4" ht="208" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+    <row r="14" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+    <row r="15" spans="1:4" ht="128" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="165" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:4" ht="144" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="14"/>
-    </row>
-    <row r="18" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="1:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="14" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+    <row r="21" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="14" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A22" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="14" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="15" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+    <row r="24" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="14" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="6" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1492,39 +1496,39 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E60"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>173</v>
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B3" t="s">
@@ -1537,8 +1541,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
@@ -1551,8 +1555,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B5" t="s">
@@ -1565,8 +1569,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B6" t="s">
@@ -1579,8 +1583,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B7" t="s">
@@ -1593,8 +1597,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>59</v>
       </c>
       <c r="B8" t="s">
@@ -1607,8 +1611,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>61</v>
       </c>
       <c r="B9" t="s">
@@ -1621,8 +1625,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>63</v>
       </c>
       <c r="B10" t="s">
@@ -1635,8 +1639,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>65</v>
       </c>
       <c r="B11" t="s">
@@ -1649,8 +1653,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>67</v>
       </c>
       <c r="B12" t="s">
@@ -1663,8 +1667,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B13" t="s">
@@ -1677,8 +1681,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>72</v>
       </c>
       <c r="B14" t="s">
@@ -1691,8 +1695,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>74</v>
       </c>
       <c r="B15" t="s">
@@ -1705,8 +1709,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B16" t="s">
@@ -1719,8 +1723,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>78</v>
       </c>
       <c r="B17" t="s">
@@ -1733,8 +1737,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>80</v>
       </c>
       <c r="B18" t="s">
@@ -1747,8 +1751,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B19" t="s">
@@ -1761,8 +1765,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>84</v>
       </c>
       <c r="B20" t="s">
@@ -1775,8 +1779,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B21" t="s">
@@ -1789,8 +1793,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>89</v>
       </c>
       <c r="B22" t="s">
@@ -1803,8 +1807,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B23" t="s">
@@ -1817,8 +1821,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B24" t="s">
@@ -1831,8 +1835,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>96</v>
       </c>
       <c r="B25" t="s">
@@ -1845,8 +1849,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B26" t="s">
@@ -1859,8 +1863,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B27" t="s">
@@ -1873,8 +1877,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B28" t="s">
@@ -1887,8 +1891,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B29" t="s">
@@ -1901,8 +1905,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B30" t="s">
@@ -1915,8 +1919,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>109</v>
       </c>
       <c r="B31" t="s">
@@ -1929,8 +1933,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>111</v>
       </c>
       <c r="B32" t="s">
@@ -1943,8 +1947,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
         <v>113</v>
       </c>
       <c r="B33" t="s">
@@ -1957,8 +1961,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B34" t="s">
@@ -1971,8 +1975,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B35" t="s">
@@ -1985,8 +1989,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
         <v>120</v>
       </c>
       <c r="B36" t="s">
@@ -1999,8 +2003,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
         <v>122</v>
       </c>
       <c r="B37" t="s">
@@ -2013,8 +2017,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
         <v>125</v>
       </c>
       <c r="B38" t="s">
@@ -2027,8 +2031,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
         <v>127</v>
       </c>
       <c r="B39" t="s">
@@ -2041,8 +2045,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
         <v>129</v>
       </c>
       <c r="B40" t="s">
@@ -2055,8 +2059,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
         <v>131</v>
       </c>
       <c r="B41" t="s">
@@ -2069,8 +2073,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
         <v>133</v>
       </c>
       <c r="B42" t="s">
@@ -2083,8 +2087,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
         <v>135</v>
       </c>
       <c r="B43" t="s">
@@ -2097,8 +2101,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
         <v>137</v>
       </c>
       <c r="B44" t="s">
@@ -2111,8 +2115,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
         <v>140</v>
       </c>
       <c r="B45" t="s">
@@ -2125,8 +2129,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
         <v>142</v>
       </c>
       <c r="B46" t="s">
@@ -2139,8 +2143,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
         <v>144</v>
       </c>
       <c r="B47" t="s">
@@ -2153,8 +2157,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
         <v>146</v>
       </c>
       <c r="B48" t="s">
@@ -2167,8 +2171,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
         <v>148</v>
       </c>
       <c r="B49" t="s">
@@ -2181,8 +2185,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
         <v>150</v>
       </c>
       <c r="B50" t="s">
@@ -2195,8 +2199,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
         <v>152</v>
       </c>
       <c r="B51" t="s">
@@ -2209,8 +2213,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
         <v>154</v>
       </c>
       <c r="B52" t="s">
@@ -2223,8 +2227,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
         <v>156</v>
       </c>
       <c r="B53" t="s">
@@ -2237,8 +2241,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
         <v>158</v>
       </c>
       <c r="B54" t="s">
@@ -2251,8 +2255,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
         <v>160</v>
       </c>
       <c r="B55" t="s">
@@ -2265,8 +2269,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
         <v>163</v>
       </c>
       <c r="B56" t="s">
@@ -2279,8 +2283,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B57" t="s">
@@ -2293,8 +2297,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B58" t="s">
@@ -2307,8 +2311,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
       <c r="B59" t="s">
@@ -2321,8 +2325,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
         <v>171</v>
       </c>
       <c r="B60" t="s">
@@ -2340,24 +2344,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="25.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.140625" style="6"/>
-    <col min="2" max="2" width="40.140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="65.7109375" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="25.140625" style="6"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004A9683C9214F8A4BB1F1EF9AD22C56FF" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="878f7be41b7cda42cdb6ef61d6ac5132">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4aeb20c0e3442673af7ee10786458764">
     <xsd:element name="properties">
@@ -2406,15 +2402,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <documentManagement/>
@@ -2422,6 +2409,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7781E663-F24C-458A-8DF2-3318075FAF9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C6499D0-C86A-44FC-9568-A103C0481D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2432,14 +2427,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7781E663-F24C-458A-8DF2-3318075FAF9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
